--- a/data/cruz_pampa_yapatera.xlsx
+++ b/data/cruz_pampa_yapatera.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,25 +457,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -500,18 +515,27 @@
         <v>16</v>
       </c>
       <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51</v>
+      </c>
+      <c r="I2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>18</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>18</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>12</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -537,15 +561,24 @@
         <v>13</v>
       </c>
       <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" t="n">
         <v>16</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -568,18 +601,27 @@
         <v>13</v>
       </c>
       <c r="F4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>39</v>
+      </c>
+      <c r="I4" t="n">
         <v>13</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>17</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>17</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -605,15 +647,24 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>21</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -636,18 +687,27 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>17</v>
       </c>
       <c r="H6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" t="n">
         <v>16</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>12</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -673,15 +733,24 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
         <v>14</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>16</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>16</v>
       </c>
     </row>
@@ -707,15 +776,24 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -738,18 +816,27 @@
         <v>12</v>
       </c>
       <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
         <v>14</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>16</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -775,15 +862,24 @@
         <v>14</v>
       </c>
       <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>42</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
         <v>19</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -806,18 +902,27 @@
         <v>17</v>
       </c>
       <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>14</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>19</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>13</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>17</v>
       </c>
     </row>
@@ -832,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,25 +968,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -911,25 +1031,40 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -968,20 +1103,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1015,25 +1165,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1066,18 +1231,29 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1111,25 +1287,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1168,20 +1359,35 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1218,18 +1424,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1263,25 +1484,40 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1316,20 +1552,35 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1363,25 +1614,40 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/cruz_pampa_yapatera.xlsx
+++ b/data/cruz_pampa_yapatera.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,25 +472,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -524,18 +534,24 @@
         <v>51</v>
       </c>
       <c r="I2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>18</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>18</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>12</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -567,18 +583,24 @@
         <v>32</v>
       </c>
       <c r="I3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" t="n">
         <v>13</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>16</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>17</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>12</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -610,18 +632,24 @@
         <v>39</v>
       </c>
       <c r="I4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>17</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>17</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>10</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -653,18 +681,24 @@
         <v>33</v>
       </c>
       <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>21</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>9</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -696,18 +730,24 @@
         <v>31</v>
       </c>
       <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>17</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>16</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>12</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -739,20 +779,26 @@
         <v>26</v>
       </c>
       <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>16</v>
-      </c>
-      <c r="L7" t="n">
-        <v>12</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
+      <c r="N7" t="n">
+        <v>12</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -782,18 +828,24 @@
         <v>13</v>
       </c>
       <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>32</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -825,18 +877,24 @@
         <v>14</v>
       </c>
       <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
         <v>14</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>19</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>16</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>10</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -868,18 +926,24 @@
         <v>42</v>
       </c>
       <c r="I10" t="n">
+        <v>38</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
         <v>14</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>19</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>20</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>9</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -911,18 +975,24 @@
         <v>35</v>
       </c>
       <c r="I11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>14</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>19</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>13</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>17</v>
       </c>
     </row>
@@ -937,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,25 +1053,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1046,25 +1126,35 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1113,25 +1203,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1180,25 +1280,35 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1241,19 +1351,29 @@
           <t>33</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1302,25 +1422,35 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1369,25 +1499,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1436,21 +1576,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1499,25 +1649,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1562,25 +1722,35 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1629,25 +1799,35 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/cruz_pampa_yapatera.xlsx
+++ b/data/cruz_pampa_yapatera.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,25 +482,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,18 +545,21 @@
         <v>20</v>
       </c>
       <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
         <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>18</v>
       </c>
       <c r="M2" t="n">
         <v>18</v>
       </c>
       <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
         <v>12</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -589,18 +597,21 @@
         <v>26</v>
       </c>
       <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
         <v>13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>16</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>17</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>12</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -638,18 +649,21 @@
         <v>27</v>
       </c>
       <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>13</v>
-      </c>
-      <c r="L4" t="n">
-        <v>17</v>
       </c>
       <c r="M4" t="n">
         <v>17</v>
       </c>
       <c r="N4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O4" t="n">
         <v>10</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -687,18 +701,21 @@
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>21</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>9</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -736,18 +753,21 @@
         <v>24</v>
       </c>
       <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
         <v>10</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>17</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>16</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>12</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -785,18 +805,21 @@
         <v>18</v>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>14</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>16</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>12</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>16</v>
       </c>
     </row>
@@ -834,18 +857,21 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>32</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>10</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -883,18 +909,21 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
         <v>14</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>19</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>16</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>10</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -932,18 +961,21 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
         <v>14</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>20</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>9</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -981,18 +1013,21 @@
         <v>17</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>14</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>19</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>13</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1007,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,25 +1098,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1136,25 +1176,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1213,25 +1258,30 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1290,25 +1340,30 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1361,19 +1416,24 @@
           <t>12</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1432,25 +1492,30 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1509,25 +1574,30 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1586,21 +1656,26 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1659,25 +1734,30 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1732,25 +1812,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1807,27 +1892,28 @@
           <t>17</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/cruz_pampa_yapatera.xlsx
+++ b/data/cruz_pampa_yapatera.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -548,18 +553,21 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M2" t="n">
         <v>10</v>
-      </c>
-      <c r="M2" t="n">
-        <v>18</v>
       </c>
       <c r="N2" t="n">
         <v>18</v>
       </c>
       <c r="O2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P2" t="n">
         <v>12</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -600,18 +608,21 @@
         <v>5</v>
       </c>
       <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="n">
         <v>13</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>16</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>17</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
         <v>13</v>
-      </c>
-      <c r="M4" t="n">
-        <v>17</v>
       </c>
       <c r="N4" t="n">
         <v>17</v>
       </c>
       <c r="O4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P4" t="n">
         <v>10</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -704,18 +718,21 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>21</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>9</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -756,18 +773,21 @@
         <v>3</v>
       </c>
       <c r="L6" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" t="n">
         <v>10</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>17</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>16</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>12</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -808,18 +828,21 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>14</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>16</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>12</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>16</v>
       </c>
     </row>
@@ -860,18 +883,21 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>32</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -912,108 +938,114 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
         <v>14</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>19</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>16</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>10</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>PAZ ANASTACIO JUANITA ROSA</t>
+          <t>NIMA CRUZ ANA GRACIELA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>14</v>
-      </c>
       <c r="M10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>PULACHE LAZO VILMA YOHANA</t>
+          <t>PAZ ANASTACIO JUANITA ROSA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>42</v>
+      </c>
+      <c r="I11" t="n">
+        <v>38</v>
+      </c>
+      <c r="J11" t="n">
         <v>12</v>
       </c>
-      <c r="E11" t="n">
-        <v>17</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" t="n">
-        <v>35</v>
-      </c>
-      <c r="I11" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>8</v>
@@ -1025,9 +1057,67 @@
         <v>19</v>
       </c>
       <c r="O11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>PULACHE LAZO VILMA YOHANA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14</v>
+      </c>
+      <c r="O12" t="n">
+        <v>19</v>
+      </c>
+      <c r="P12" t="n">
         <v>13</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1042,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,25 +1193,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1181,25 +1276,30 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1263,25 +1363,30 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1345,25 +1450,30 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1421,19 +1531,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1497,25 +1612,30 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1579,25 +1699,30 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1659,23 +1784,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1739,25 +1865,30 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1766,154 +1897,191 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>PAZ ANASTACIO JUANITA ROSA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>NIMA CRUZ ANA GRACIELA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>PAZ ANASTACIO JUANITA ROSA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
           <t>PULACHE LAZO VILMA YOHANA</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/cruz_pampa_yapatera.xlsx
+++ b/data/cruz_pampa_yapatera.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -556,18 +571,27 @@
         <v>21</v>
       </c>
       <c r="M2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
         <v>10</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>18</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>18</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>12</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -611,18 +635,27 @@
         <v>8</v>
       </c>
       <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
         <v>13</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>16</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>17</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>12</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -666,18 +699,27 @@
         <v>9</v>
       </c>
       <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
         <v>13</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>17</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>17</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -721,18 +763,27 @@
         <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>21</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>9</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -776,18 +827,27 @@
         <v>19</v>
       </c>
       <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
         <v>10</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>17</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>16</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -831,18 +891,27 @@
         <v>8</v>
       </c>
       <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>14</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>16</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>12</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>16</v>
       </c>
     </row>
@@ -886,18 +955,27 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>10</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>32</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -941,18 +1019,27 @@
         <v>9</v>
       </c>
       <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
         <v>14</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>19</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>16</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1010,6 +1097,15 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1051,18 +1147,27 @@
         <v>8</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>14</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>19</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>20</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1106,18 +1211,27 @@
         <v>11</v>
       </c>
       <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>14</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>19</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1132,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,25 +1312,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1281,25 +1410,40 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1368,25 +1512,40 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1455,25 +1614,40 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1536,19 +1710,34 @@
           <t>8</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1617,25 +1806,36 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1704,25 +1904,40 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1787,21 +2002,36 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1870,25 +2100,40 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1920,6 +2165,9 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1978,27 +2226,34 @@
           <t>8</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2063,25 +2318,36 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
